--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,236 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F8" s="3">
         <v>33100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>24400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>23800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>20300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>15700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>7700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F9" s="3">
         <v>14700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>11900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>10100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>8200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F10" s="3">
         <v>18400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>12500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>10700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>10200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>7700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-1300</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-1700</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,58 +929,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E12" s="3">
         <v>11600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G12" s="3">
         <v>10700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>9700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>7600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>5100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>9000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>16300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,26 +1037,32 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,11 +1075,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1054,8 +1093,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1172,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>60700</v>
+      </c>
+      <c r="F17" s="3">
         <v>58700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>52800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>52100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>42500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>34600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>29900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>27000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>21500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>40200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>55500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>13100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>26000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-28400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-28300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-22200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-17900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-15700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-24500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-47800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-11000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-23600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,34 +1306,36 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1277,172 +1344,196 @@
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-23700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-26800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-26600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-20500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-17000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-15000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-16100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-22700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-44900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-22200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
         <v>1000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1400</v>
       </c>
       <c r="J22" s="3">
         <v>1400</v>
       </c>
       <c r="K22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>2100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-25300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-28500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-28200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-22600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-19200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-18300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-14100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-27400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-53000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-25700</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1582,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1638,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-25300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-28500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-28200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-18300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-14100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-27400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-53000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-25700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-25300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-28500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-28200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-22600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-19200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-18300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-14100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-53000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-25700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,34 +1974,40 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -1877,72 +2016,84 @@
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-25300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-28500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-28200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-18300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-14100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-53000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-25700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2142,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-25300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-28500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-28200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-18300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-14100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-53000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-25700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,44 +2307,46 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>257200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>287100</v>
+      </c>
+      <c r="F41" s="3">
         <v>149700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>181000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>221900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>249200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>269800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>284300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>304300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>320500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>159200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2359,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,44 +2415,50 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>34600</v>
+      </c>
+      <c r="F43" s="3">
         <v>33200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>20600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>12800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>10900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,44 +2471,50 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F44" s="3">
         <v>42600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>38900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>28500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>22400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>13800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>13200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>14000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>10700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>10700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2336,44 +2527,50 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,44 +2583,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>350600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>368700</v>
+      </c>
+      <c r="F46" s="3">
         <v>230000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>245600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>272600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>288900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>298300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>308000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>326200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>339500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>176500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,8 +2639,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2486,44 +2695,50 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>47700</v>
+      </c>
+      <c r="F48" s="3">
         <v>37900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>34400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>32100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>29500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>10500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,44 +2751,50 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G49" s="3">
         <v>1400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,8 +2807,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,44 +2919,50 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,8 +2975,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,44 +3031,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>421100</v>
+      </c>
+      <c r="F54" s="3">
         <v>272400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>284500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>309300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>324000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>310900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>320900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>337000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>351500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>190600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +3087,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,44 +3135,46 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3187,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2976,44 +3243,50 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25900</v>
+        <v>32400</v>
       </c>
       <c r="E59" s="3">
-        <v>22200</v>
+        <v>27800</v>
       </c>
       <c r="F59" s="3">
         <v>25900</v>
       </c>
       <c r="G59" s="3">
+        <v>22200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I59" s="3">
         <v>21000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,44 +3299,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F60" s="3">
         <v>35900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>35300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>27400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>18600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>16200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3355,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3085,35 +3370,35 @@
         <v>51300</v>
       </c>
       <c r="E61" s="3">
+        <v>51300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>51300</v>
+      </c>
+      <c r="G61" s="3">
         <v>51200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>51200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>50700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>50500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>50300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>50000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>49800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>49500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3126,44 +3411,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>29100</v>
+      </c>
+      <c r="F62" s="3">
         <v>29300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>27600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>25800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>25200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3467,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,44 +3635,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>121800</v>
+      </c>
+      <c r="F66" s="3">
         <v>116500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>111300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>112300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>103300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>71700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>68200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>69900</v>
       </c>
       <c r="K66" s="3">
         <v>68200</v>
       </c>
       <c r="L66" s="3">
+        <v>69900</v>
+      </c>
+      <c r="M66" s="3">
+        <v>68200</v>
+      </c>
+      <c r="N66" s="3">
         <v>68300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3691,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3526,14 +3861,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>328600</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,44 +3937,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-454600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-427100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-402400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-377200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-348700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-320500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-297900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-278700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-261500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-243200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-229100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,44 +4161,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>280800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>299400</v>
+      </c>
+      <c r="F76" s="3">
         <v>155900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>173100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>197100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>220800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>239200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>252800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>267100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>283300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-206300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4273,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-25300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-28500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-28200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-18300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-14100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-53000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-25700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,47 +4416,49 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4468,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,47 +4748,53 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-28300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-35900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-25200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-19900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-17100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-18200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-16500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-28100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-48300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4371,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,47 +4830,49 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,47 +4994,53 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-300</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,47 +5296,53 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>162100</v>
+      </c>
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>174100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>87400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>106800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4861,8 +5352,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4911,47 +5408,53 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>137400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-31300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-40900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-27400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-20600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-14500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-16200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>161300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>59100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>58200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,6 +5462,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,261 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E8" s="3">
         <v>43600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E9" s="3">
         <v>22300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E10" s="3">
         <v>21300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1300</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>-1700</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,64 +944,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E12" s="3">
         <v>14500</v>
-      </c>
-      <c r="E12" s="3">
-        <v>11600</v>
       </c>
       <c r="F12" s="3">
         <v>11600</v>
       </c>
       <c r="G12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="H12" s="3">
         <v>10700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,16 +1060,19 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1060,12 +1080,12 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>3300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,8 +1101,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,120 +1200,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E17" s="3">
         <v>73100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>58700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-25600</v>
       </c>
       <c r="F18" s="3">
         <v>-25600</v>
       </c>
       <c r="G18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="H18" s="3">
         <v>-28400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-22200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-47800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,55 +1341,56 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1000</v>
       </c>
       <c r="I20" s="3">
         <v>1000</v>
       </c>
       <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1364,87 +1398,93 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-25100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-22700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-44900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-22200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1000</v>
       </c>
       <c r="F22" s="3">
         <v>1000</v>
       </c>
       <c r="G22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>900</v>
       </c>
       <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
         <v>1500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1400</v>
       </c>
       <c r="K22" s="3">
         <v>1400</v>
@@ -1453,87 +1493,93 @@
         <v>1400</v>
       </c>
       <c r="M22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-53000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25700</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-27400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-53000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-53000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,55 +2047,58 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1000</v>
       </c>
       <c r="I32" s="3">
         <v>-1000</v>
       </c>
       <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2036,64 +2106,70 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-53000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-53000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,47 +2395,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E41" s="3">
         <v>257200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>287100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>181000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>221900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>249200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>269800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>284300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>304300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>320500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>159200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2452,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,47 +2511,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E43" s="3">
         <v>48400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>34600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,46 +2570,49 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E44" s="3">
         <v>39800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>42200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>42600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>38900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>28500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>22400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>10700</v>
       </c>
       <c r="N44" s="3">
         <v>10700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+      <c r="O44" s="3">
+        <v>10700</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -2533,47 +2629,50 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E45" s="3">
         <v>5200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,47 +2688,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E46" s="3">
         <v>350600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>368700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>230000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>245600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>272600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>288900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>298300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>308000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>326200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>339500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>176500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2701,47 +2806,50 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E48" s="3">
         <v>49000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>47700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,47 +2865,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1300</v>
       </c>
       <c r="F49" s="3">
         <v>1300</v>
       </c>
       <c r="G49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H49" s="3">
         <v>1400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1500</v>
       </c>
       <c r="I49" s="3">
         <v>1500</v>
       </c>
       <c r="J49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K49" s="3">
         <v>1600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1800</v>
       </c>
       <c r="M49" s="3">
         <v>1800</v>
       </c>
       <c r="N49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O49" s="3">
         <v>1900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,47 +3042,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3100</v>
       </c>
       <c r="H52" s="3">
         <v>3100</v>
       </c>
       <c r="I52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>800</v>
       </c>
       <c r="N52" s="3">
+        <v>800</v>
+      </c>
+      <c r="O52" s="3">
         <v>1700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,47 +3160,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>382900</v>
+      </c>
+      <c r="E54" s="3">
         <v>404700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>421100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>272400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>284500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>309300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>324000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>310900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>320900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>337000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>351500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>190600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,47 +3267,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E57" s="3">
         <v>13500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3249,47 +3383,50 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E59" s="3">
         <v>32400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,47 +3442,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E60" s="3">
         <v>45900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,13 +3501,16 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51300</v>
+        <v>51400</v>
       </c>
       <c r="E61" s="3">
         <v>51300</v>
@@ -3376,32 +3519,32 @@
         <v>51300</v>
       </c>
       <c r="G61" s="3">
-        <v>51200</v>
+        <v>51300</v>
       </c>
       <c r="H61" s="3">
         <v>51200</v>
       </c>
       <c r="I61" s="3">
+        <v>51200</v>
+      </c>
+      <c r="J61" s="3">
         <v>50700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>49800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>49500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3417,47 +3560,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E62" s="3">
         <v>26700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>29100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,47 +3796,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E66" s="3">
         <v>124000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>121800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>116500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>111300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>112300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>103300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3867,11 +4035,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>328600</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,47 +4114,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-480500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-454600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-427100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-402400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-377200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-348700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-320500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-297900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-278700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-261500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-243200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-229100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,47 +4350,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E76" s="3">
         <v>280800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>299400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>155900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>173100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>197100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>220800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>239200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>252800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>267100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>283300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-206300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-53000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,25 +4616,26 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
@@ -4445,7 +4644,7 @@
         <v>700</v>
       </c>
       <c r="K83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
@@ -4454,14 +4653,14 @@
         <v>800</v>
       </c>
       <c r="N83" s="3">
+        <v>800</v>
+      </c>
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,50 +4968,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-48300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,50 +5052,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,50 +5227,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,50 +5545,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E100" s="3">
         <v>2900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>162100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>174100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>87400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>106800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5414,50 +5663,53 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>137400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-31300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>161300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>59100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>58200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,274 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E8" s="3">
         <v>44500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>43600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E9" s="3">
         <v>19500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E10" s="3">
         <v>25000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>-1700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E12" s="3">
         <v>13100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>11600</v>
       </c>
       <c r="G12" s="3">
         <v>11600</v>
       </c>
       <c r="H12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I12" s="3">
         <v>10700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,19 +1080,22 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1083,12 +1103,12 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>3300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1124,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E17" s="3">
         <v>72200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>73100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>60700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>58700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-25600</v>
       </c>
       <c r="G18" s="3">
         <v>-25600</v>
       </c>
       <c r="H18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-28400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,58 +1375,59 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1000</v>
       </c>
       <c r="J20" s="3">
         <v>1000</v>
       </c>
       <c r="K20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1401,67 +1435,73 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-25100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-23700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-22700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-44900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-22200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1469,25 +1509,25 @@
         <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1000</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
       </c>
       <c r="H22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I22" s="3">
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>1500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1400</v>
       </c>
       <c r="L22" s="3">
         <v>1400</v>
@@ -1496,90 +1536,96 @@
         <v>1400</v>
       </c>
       <c r="N22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-26000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-22600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-26000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-22600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,58 +2117,61 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1000</v>
       </c>
       <c r="J32" s="3">
         <v>-1000</v>
       </c>
       <c r="K32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2109,67 +2179,73 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-22600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-22600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,50 +2482,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>214100</v>
+      </c>
+      <c r="E41" s="3">
         <v>225600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>257200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>287100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>149700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>181000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>221900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>249200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>269800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>284300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>304300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>320500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>159200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2542,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,50 +2604,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E43" s="3">
         <v>56100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>33200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,49 +2666,52 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E44" s="3">
         <v>41600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>39800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>42200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>42600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>38900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>28500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>10700</v>
       </c>
       <c r="O44" s="3">
         <v>10700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="P44" s="3">
+        <v>10700</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
@@ -2632,50 +2728,53 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,50 +2790,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>321900</v>
+      </c>
+      <c r="E46" s="3">
         <v>329200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>350600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>368700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>230000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>245600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>272600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>288900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>298300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>308000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>326200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>339500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>176500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2809,50 +2914,53 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E48" s="3">
         <v>48400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2877,41 +2988,41 @@
         <v>1100</v>
       </c>
       <c r="E49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F49" s="3">
         <v>1200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1300</v>
       </c>
       <c r="G49" s="3">
         <v>1300</v>
       </c>
       <c r="H49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I49" s="3">
         <v>1400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1500</v>
       </c>
       <c r="J49" s="3">
         <v>1500</v>
       </c>
       <c r="K49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L49" s="3">
         <v>1600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1800</v>
       </c>
       <c r="N49" s="3">
         <v>1800</v>
       </c>
       <c r="O49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P49" s="3">
         <v>1900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,50 +3162,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E52" s="3">
         <v>4200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3100</v>
       </c>
       <c r="I52" s="3">
         <v>3100</v>
       </c>
       <c r="J52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3800</v>
-      </c>
-      <c r="M52" s="3">
-        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>800</v>
       </c>
       <c r="O52" s="3">
+        <v>800</v>
+      </c>
+      <c r="P52" s="3">
         <v>1700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,50 +3286,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>374400</v>
+      </c>
+      <c r="E54" s="3">
         <v>382900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>404700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>421100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>272400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>284500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>309300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>324000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>310900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>320900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>351500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>190600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,50 +3398,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3386,50 +3520,53 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E59" s="3">
         <v>28600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,50 +3582,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E60" s="3">
         <v>38700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13800</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,8 +3644,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3513,7 +3656,7 @@
         <v>51400</v>
       </c>
       <c r="E61" s="3">
-        <v>51300</v>
+        <v>51400</v>
       </c>
       <c r="F61" s="3">
         <v>51300</v>
@@ -3522,32 +3665,32 @@
         <v>51300</v>
       </c>
       <c r="H61" s="3">
-        <v>51200</v>
+        <v>51300</v>
       </c>
       <c r="I61" s="3">
         <v>51200</v>
       </c>
       <c r="J61" s="3">
+        <v>51200</v>
+      </c>
+      <c r="K61" s="3">
         <v>50700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>49800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>49500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3563,50 +3706,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E62" s="3">
         <v>28800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,50 +3954,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E66" s="3">
         <v>118900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>124000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>121800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>116500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>111300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>68200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4038,11 +4206,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>328600</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,50 +4288,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-506200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-480500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-454600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-427100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-402400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-377200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-348700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-320500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-297900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-278700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-261500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-243200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-229100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,50 +4536,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E76" s="3">
         <v>264000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>280800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>299400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>155900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>173100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>197100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>220800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>239200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>252800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>267100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>283300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-206300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-22600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,28 +4815,29 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
@@ -4647,7 +4846,7 @@
         <v>700</v>
       </c>
       <c r="L83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>800</v>
@@ -4656,14 +4855,14 @@
         <v>800</v>
       </c>
       <c r="O83" s="3">
+        <v>800</v>
+      </c>
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,53 +5185,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,53 +5273,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,53 +5457,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,53 +5791,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E100" s="3">
         <v>2600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>162100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>174100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>87400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>106800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5666,53 +5915,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-31600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>137400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-31300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>161300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>59100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>58200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +5975,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E8" s="3">
         <v>53400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>44500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>43600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E9" s="3">
         <v>21900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E10" s="3">
         <v>31500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1300</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>-1700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E12" s="3">
         <v>17500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>11600</v>
       </c>
       <c r="H12" s="3">
         <v>11600</v>
       </c>
       <c r="I12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7800</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,8 +1114,8 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1106,12 +1126,12 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1127,8 +1147,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1145,31 +1165,34 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E17" s="3">
         <v>80200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>72200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>73100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>60700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>52100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-26800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-27700</v>
-      </c>
       <c r="F18" s="3">
-        <v>-29500</v>
+        <v>-27600</v>
       </c>
       <c r="G18" s="3">
-        <v>-25600</v>
+        <v>-29600</v>
       </c>
       <c r="H18" s="3">
         <v>-25600</v>
       </c>
       <c r="I18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-28400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-22200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-47800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,61 +1409,62 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2200</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>1000</v>
       </c>
       <c r="L20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1438,99 +1472,105 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-23300</v>
+        <v>-21000</v>
       </c>
       <c r="E21" s="3">
-        <v>-23700</v>
+        <v>-25600</v>
       </c>
       <c r="F21" s="3">
-        <v>-25100</v>
+        <v>-26500</v>
       </c>
       <c r="G21" s="3">
-        <v>-22500</v>
+        <v>-28400</v>
       </c>
       <c r="H21" s="3">
-        <v>-23700</v>
+        <v>-24500</v>
       </c>
       <c r="I21" s="3">
-        <v>-26800</v>
+        <v>-25000</v>
       </c>
       <c r="J21" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-26600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-44900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-22200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E22" s="3">
         <v>1000</v>
       </c>
       <c r="F22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="3">
         <v>1100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>1000</v>
       </c>
       <c r="I22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J22" s="3">
         <v>900</v>
       </c>
       <c r="K22" s="3">
+        <v>900</v>
+      </c>
+      <c r="L22" s="3">
         <v>1500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1400</v>
       </c>
       <c r="M22" s="3">
         <v>1400</v>
@@ -1539,116 +1579,122 @@
         <v>1400</v>
       </c>
       <c r="O22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-53000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25700</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,61 +2187,64 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2200</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-2000</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-1000</v>
       </c>
       <c r="L32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2182,70 +2252,76 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>196800</v>
+      </c>
+      <c r="E41" s="3">
         <v>214100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>225600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>257200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>287100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>149700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>181000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>221900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>249200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>269800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>284300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>304300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>320500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>159200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,53 +2697,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E43" s="3">
         <v>58900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>56100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,52 +2762,55 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E44" s="3">
         <v>43900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>39800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>42200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>42600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>38900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>28500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>10700</v>
       </c>
       <c r="P44" s="3">
         <v>10700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3">
+        <v>10700</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
@@ -2731,53 +2827,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L45" s="3">
         <v>4500</v>
       </c>
-      <c r="I45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4500</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E46" s="3">
         <v>321900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>329200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>350600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>368700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>230000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>245600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>272600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>288900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>298300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>308000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>326200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>339500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>176500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,31 +2957,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2917,53 +3022,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E48" s="3">
         <v>47300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,53 +3087,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
         <v>1100</v>
       </c>
       <c r="F49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G49" s="3">
         <v>1200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1300</v>
       </c>
       <c r="H49" s="3">
         <v>1300</v>
       </c>
       <c r="I49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J49" s="3">
         <v>1400</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1500</v>
       </c>
       <c r="K49" s="3">
         <v>1500</v>
       </c>
       <c r="L49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1800</v>
       </c>
       <c r="O49" s="3">
         <v>1800</v>
       </c>
       <c r="P49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,53 +3282,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>4100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3100</v>
       </c>
       <c r="J52" s="3">
         <v>3100</v>
       </c>
       <c r="K52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L52" s="3">
         <v>4000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>800</v>
       </c>
       <c r="O52" s="3">
         <v>800</v>
       </c>
       <c r="P52" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>374100</v>
+      </c>
+      <c r="E54" s="3">
         <v>374400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>382900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>404700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>421100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>272400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>284500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>309300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>324000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>310900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>320900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>351500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>190600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,53 +3529,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,31 +3592,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3523,53 +3657,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>32900</v>
+        <v>15900</v>
       </c>
       <c r="E59" s="3">
-        <v>28600</v>
+        <v>14300</v>
       </c>
       <c r="F59" s="3">
-        <v>32400</v>
+        <v>13500</v>
       </c>
       <c r="G59" s="3">
-        <v>27800</v>
+        <v>7300</v>
       </c>
       <c r="H59" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>13600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="K59" s="3">
         <v>25900</v>
       </c>
-      <c r="I59" s="3">
-        <v>22200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>25900</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E60" s="3">
         <v>42800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13800</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,53 +3787,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51400</v>
+        <v>78800</v>
       </c>
       <c r="E61" s="3">
-        <v>51400</v>
+        <v>79200</v>
       </c>
       <c r="F61" s="3">
-        <v>51300</v>
+        <v>79700</v>
       </c>
       <c r="G61" s="3">
-        <v>51300</v>
+        <v>77500</v>
       </c>
       <c r="H61" s="3">
-        <v>51300</v>
+        <v>79900</v>
       </c>
       <c r="I61" s="3">
+        <v>80200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>78800</v>
+      </c>
+      <c r="K61" s="3">
         <v>51200</v>
       </c>
-      <c r="J61" s="3">
-        <v>51200</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>49800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>49500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,53 +3852,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28300</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>28800</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>26700</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>29100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>29300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>27600</v>
-      </c>
-      <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>25800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E66" s="3">
         <v>122600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>118900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>124000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>121800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>116500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>111300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>112300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>69900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4209,11 +4377,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>328600</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-527100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-506200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-480500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-454600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-427100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-402400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-377200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-348700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-320500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-297900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-278700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-261500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-243200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-229100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>241200</v>
+      </c>
+      <c r="E76" s="3">
         <v>251800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>264000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>280800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>299400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>155900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>173100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>197100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>220800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>239200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>252800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>283300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-206300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,31 +5014,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
@@ -4849,7 +5048,7 @@
         <v>700</v>
       </c>
       <c r="M83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
@@ -4858,14 +5057,14 @@
         <v>800</v>
       </c>
       <c r="P83" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2900</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,56 +5402,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-35900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-48300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,56 +5494,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,56 +5687,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,56 +6037,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>162100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>174100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>87400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>106800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,31 +6102,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5918,56 +6167,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>137400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>161300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>59100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>58200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,300 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E8" s="3">
         <v>58400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>43600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E9" s="3">
         <v>21500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E10" s="3">
         <v>36900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1300</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>-1700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +985,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E12" s="3">
         <v>16600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>11600</v>
       </c>
       <c r="I12" s="3">
         <v>11600</v>
       </c>
       <c r="J12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K12" s="3">
         <v>10700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1129,12 +1148,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>3300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1150,8 +1169,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1168,35 +1187,38 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
         <v>1300</v>
       </c>
       <c r="F15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1280,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E17" s="3">
         <v>80800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>80200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>72200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>73100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>60700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>52800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-29600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-25600</v>
       </c>
       <c r="I18" s="3">
         <v>-25600</v>
       </c>
       <c r="J18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-28400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-22200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-47800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,25 +1442,26 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1437,37 +1470,37 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>1000</v>
       </c>
       <c r="M20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1475,105 +1508,111 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-25600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-28400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-24500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-27600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-22700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-44900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-22200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1000</v>
       </c>
       <c r="F22" s="3">
         <v>1000</v>
       </c>
       <c r="G22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="3">
         <v>1100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1000</v>
       </c>
       <c r="I22" s="3">
         <v>1000</v>
       </c>
       <c r="J22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
       </c>
       <c r="L22" s="3">
+        <v>900</v>
+      </c>
+      <c r="M22" s="3">
         <v>1500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1400</v>
       </c>
       <c r="N22" s="3">
         <v>1400</v>
@@ -1582,96 +1621,102 @@
         <v>1400</v>
       </c>
       <c r="P22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-53000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-25700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1696,8 +1741,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1848,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-26000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-22600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-53000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-25700</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-26000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-22600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-53000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-25700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,25 +2256,28 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2217,37 +2286,37 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-1000</v>
       </c>
       <c r="M32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2255,73 +2324,79 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-26000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-22600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-53000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-25700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2460,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-26000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-22600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-53000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-25700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2655,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>333700</v>
+      </c>
+      <c r="E41" s="3">
         <v>196800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>214100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>225600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>257200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>287100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>149700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>181000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>221900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>249200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>269800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>284300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>304300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>320500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>159200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,56 +2789,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E43" s="3">
         <v>69000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>56100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,55 +2857,58 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E44" s="3">
         <v>50900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>43900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>41600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>39800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>42200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>42600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>38900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>28500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14000</v>
-      </c>
-      <c r="P44" s="3">
-        <v>10700</v>
       </c>
       <c r="Q44" s="3">
         <v>10700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
+      <c r="R44" s="3">
+        <v>10700</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
@@ -2830,13 +2925,16 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>400</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2847,8 +2945,8 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>100</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2856,30 +2954,30 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,56 +2993,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E46" s="3">
         <v>323000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>321900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>329200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>350600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>368700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>230000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>245600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>288900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>298300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>326200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>339500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>176500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2986,8 +3090,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3025,56 +3129,59 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E48" s="3">
         <v>45900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>47300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>48400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>47700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,56 +3197,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1100</v>
       </c>
       <c r="F49" s="3">
         <v>1100</v>
       </c>
       <c r="G49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H49" s="3">
         <v>1200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1300</v>
       </c>
       <c r="I49" s="3">
         <v>1300</v>
       </c>
       <c r="J49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1400</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1500</v>
       </c>
       <c r="L49" s="3">
         <v>1500</v>
       </c>
       <c r="M49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N49" s="3">
         <v>1600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1700</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1800</v>
       </c>
       <c r="P49" s="3">
         <v>1800</v>
       </c>
       <c r="Q49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R49" s="3">
         <v>1900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,56 +3401,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4000</v>
       </c>
       <c r="H52" s="3">
         <v>3500</v>
       </c>
       <c r="I52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J52" s="3">
         <v>3200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3100</v>
       </c>
       <c r="K52" s="3">
         <v>3100</v>
       </c>
       <c r="L52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>800</v>
       </c>
       <c r="P52" s="3">
         <v>800</v>
       </c>
       <c r="Q52" s="3">
+        <v>800</v>
+      </c>
+      <c r="R52" s="3">
         <v>1700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3537,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E54" s="3">
         <v>374100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>374400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>382900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>404700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>421100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>272400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>284500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>309300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>324000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>310900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>320900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>337000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>351500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>190600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,56 +3659,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,35 +3725,38 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3600</v>
       </c>
       <c r="G58" s="3">
         <v>3600</v>
       </c>
       <c r="H58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3660,56 +3793,59 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E59" s="3">
         <v>15900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,56 +3861,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E60" s="3">
         <v>53600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13800</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,56 +3929,59 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E61" s="3">
         <v>78800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>79200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>77500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>80200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>78800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>49800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>49500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,13 +3997,16 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
@@ -3872,8 +4017,8 @@
       <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -3881,30 +4026,30 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>25800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4269,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E66" s="3">
         <v>132900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>122600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>118900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>124000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>121800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>116500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>111300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>71700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4380,11 +4547,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>328600</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4635,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-546000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-527100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-506200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-480500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-454600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-427100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-402400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-377200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-348700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-320500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-297900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-278700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-261500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-243200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-229100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +4907,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>402200</v>
+      </c>
+      <c r="E76" s="3">
         <v>241200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>251800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>264000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>280800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>299400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>155900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>173100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>197100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>220800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>239200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>252800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>283300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-206300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5043,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-26000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-22600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-53000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-25700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,34 +5212,35 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
@@ -5051,7 +5249,7 @@
         <v>700</v>
       </c>
       <c r="N83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
@@ -5060,14 +5258,14 @@
         <v>800</v>
       </c>
       <c r="Q83" s="3">
+        <v>800</v>
+      </c>
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5080,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,59 +5618,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-28100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-48300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,59 +5714,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
       <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5560,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,59 +5916,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
       </c>
       <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5755,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,8 +6039,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,59 +6282,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>170500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>162100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>174100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>87400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>106800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6131,8 +6379,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6170,59 +6418,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-31600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>137400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>161300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>59100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>58200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,312 +656,325 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E8" s="3">
         <v>68200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>53400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2400</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E9" s="3">
         <v>24600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E10" s="3">
         <v>43700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>36900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>31500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1300</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>-1700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E12" s="3">
         <v>15100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>11600</v>
       </c>
       <c r="J12" s="3">
         <v>11600</v>
       </c>
       <c r="K12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="L12" s="3">
         <v>10700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1151,12 +1171,12 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>3300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1172,8 +1192,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1199,29 +1222,29 @@
         <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3">
         <v>1300</v>
       </c>
       <c r="G15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E17" s="3">
         <v>87900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>80800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>80200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>73100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>60700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-25600</v>
       </c>
       <c r="J18" s="3">
         <v>-25600</v>
       </c>
       <c r="K18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="L18" s="3">
         <v>-28400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-22200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-47800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,29 +1476,30 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1473,37 +1507,37 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>1000</v>
       </c>
       <c r="N20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1511,111 +1545,117 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-25600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-28600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-27600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-22700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-44900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-22200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1000</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
       </c>
       <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
         <v>1100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1000</v>
       </c>
       <c r="J22" s="3">
         <v>1000</v>
       </c>
       <c r="K22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>1500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1400</v>
       </c>
       <c r="O22" s="3">
         <v>1400</v>
@@ -1624,99 +1664,105 @@
         <v>1400</v>
       </c>
       <c r="Q22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-53000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-25700</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1744,8 +1790,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-26000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-22600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-27400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-53000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-25700</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-53000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-25700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,29 +2326,32 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2289,37 +2359,37 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-1000</v>
       </c>
       <c r="N32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2327,76 +2397,82 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-27400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-25700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-27400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-25700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,59 +2742,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>316200</v>
+      </c>
+      <c r="E41" s="3">
         <v>333700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>196800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>214100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>257200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>287100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>149700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>221900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>249200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>269800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>284300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>304300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>320500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>159200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2811,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2792,59 +2882,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E43" s="3">
         <v>83500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>69000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>33200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,58 +2953,61 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E44" s="3">
         <v>56200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>50900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>43900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>41600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>39800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>42200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>42600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>28500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14000</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>10700</v>
       </c>
       <c r="R44" s="3">
         <v>10700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
+      <c r="S44" s="3">
+        <v>10700</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
@@ -2928,59 +3024,62 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,59 +3095,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>465800</v>
+      </c>
+      <c r="E46" s="3">
         <v>481800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>323000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>321900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>329200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>350600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>368700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>230000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>245600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>272600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>288900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>298300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>326200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>339500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>176500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3093,8 +3198,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3132,59 +3237,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E48" s="3">
         <v>45700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>48400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>49000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3209,50 +3320,50 @@
         <v>900</v>
       </c>
       <c r="E49" s="3">
+        <v>900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1100</v>
       </c>
       <c r="G49" s="3">
         <v>1100</v>
       </c>
       <c r="H49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I49" s="3">
         <v>1200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1300</v>
       </c>
       <c r="J49" s="3">
         <v>1300</v>
       </c>
       <c r="K49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L49" s="3">
         <v>1400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1500</v>
       </c>
       <c r="M49" s="3">
         <v>1500</v>
       </c>
       <c r="N49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O49" s="3">
         <v>1600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1800</v>
       </c>
       <c r="Q49" s="3">
         <v>1800</v>
       </c>
       <c r="R49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S49" s="3">
         <v>1900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,59 +3521,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3500</v>
       </c>
       <c r="I52" s="3">
         <v>3500</v>
       </c>
       <c r="J52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K52" s="3">
         <v>3200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3100</v>
       </c>
       <c r="L52" s="3">
         <v>3100</v>
       </c>
       <c r="M52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>800</v>
       </c>
       <c r="Q52" s="3">
         <v>800</v>
       </c>
       <c r="R52" s="3">
+        <v>800</v>
+      </c>
+      <c r="S52" s="3">
         <v>1700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,59 +3663,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>519400</v>
+      </c>
+      <c r="E54" s="3">
         <v>534000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>374100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>374400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>382900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>404700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>421100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>272400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>284500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>309300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>324000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>310900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>320900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>337000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>351500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>190600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,59 +3790,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,38 +3859,41 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3600</v>
       </c>
       <c r="H58" s="3">
         <v>3600</v>
       </c>
       <c r="I58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3796,59 +3930,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E59" s="3">
         <v>11300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,59 +4001,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E60" s="3">
         <v>53100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>41400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13800</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,59 +4072,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E61" s="3">
         <v>78300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>78800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>77500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>79900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>80200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>78800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>49800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4000,8 +4143,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4009,7 +4155,7 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>500</v>
@@ -4020,8 +4166,8 @@
       <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>500</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -4029,30 +4175,30 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>25800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,59 +4427,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>130200</v>
+      </c>
+      <c r="E66" s="3">
         <v>131800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>132900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>122600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>118900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>124000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>116500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>111300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>71700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4550,11 +4718,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>328600</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,59 +4809,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-570700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-546000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-527100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-506200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-480500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-454600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-427100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-402400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-377200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-348700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-320500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-297900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-278700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-261500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-243200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-229100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,59 +5093,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>389200</v>
+      </c>
+      <c r="E76" s="3">
         <v>402200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>241200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>251800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>264000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>299400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>155900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>173100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>197100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>220800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>239200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>252800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>267100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>283300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-206300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-27400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-25700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,37 +5411,38 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>700</v>
@@ -5252,7 +5451,7 @@
         <v>700</v>
       </c>
       <c r="O83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>800</v>
@@ -5261,14 +5460,14 @@
         <v>800</v>
       </c>
       <c r="R83" s="3">
+        <v>800</v>
+      </c>
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5835,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-28100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-48300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,62 +5935,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,62 +6146,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6276,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,62 +6528,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>170500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>162100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>174100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>87400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>106800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6382,8 +6631,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6421,62 +6670,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E102" s="3">
         <v>137000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-31600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>137400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>161300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>58200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,325 +656,338 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E8" s="3">
         <v>69200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>68200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>58400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>44500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2400</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E9" s="3">
         <v>25000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E10" s="3">
         <v>44200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>43700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1300</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <v>-1700</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E12" s="3">
         <v>16400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>11600</v>
       </c>
       <c r="K12" s="3">
         <v>11600</v>
       </c>
       <c r="L12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="M12" s="3">
         <v>10700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7800</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,12 +1194,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1195,8 +1215,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1213,41 +1233,44 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
         <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
         <v>1300</v>
       </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E17" s="3">
         <v>96600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>87900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>80800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>80200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>72200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>73100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>60700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>55500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-25600</v>
       </c>
       <c r="K18" s="3">
         <v>-25600</v>
       </c>
       <c r="L18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-28400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-47800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,32 +1510,33 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1510,37 +1544,37 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>1000</v>
       </c>
       <c r="O20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1548,79 +1582,85 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-25600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-28600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-27600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-22700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-44900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-22200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1628,37 +1668,37 @@
         <v>900</v>
       </c>
       <c r="E22" s="3">
+        <v>900</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>1000</v>
       </c>
       <c r="I22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>1000</v>
       </c>
       <c r="L22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="M22" s="3">
         <v>900</v>
       </c>
       <c r="N22" s="3">
+        <v>900</v>
+      </c>
+      <c r="O22" s="3">
         <v>1500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1400</v>
       </c>
       <c r="P22" s="3">
         <v>1400</v>
@@ -1667,102 +1707,108 @@
         <v>1400</v>
       </c>
       <c r="R22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-53000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,8 +1839,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-22600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-27400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-53000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-25700</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-27400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-53000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-25700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,32 +2396,35 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2362,37 +2432,37 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-1000</v>
       </c>
       <c r="O32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2400,79 +2470,85 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-25700</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-25700</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>302700</v>
+      </c>
+      <c r="E41" s="3">
         <v>316200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>333700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>196800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>214100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>257200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>287100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>181000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>221900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>249200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>269800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>284300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>304300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>320500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>159200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2885,62 +2975,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E43" s="3">
         <v>79300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>83500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>69000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,61 +3049,64 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E44" s="3">
         <v>62300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>56200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>50900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>41600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>39800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>42200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>42600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>10700</v>
       </c>
       <c r="S44" s="3">
         <v>10700</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
+      <c r="T44" s="3">
+        <v>10700</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>458100</v>
+      </c>
+      <c r="E46" s="3">
         <v>465800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>481800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>323000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>321900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>329200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>350600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>368700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>230000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>245600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>272600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>288900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>298300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>326200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>339500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>176500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3240,62 +3345,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E48" s="3">
         <v>46700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>48400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>49000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10500</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,62 +3419,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E49" s="3">
         <v>900</v>
       </c>
       <c r="F49" s="3">
+        <v>900</v>
+      </c>
+      <c r="G49" s="3">
         <v>1000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1100</v>
       </c>
       <c r="H49" s="3">
         <v>1100</v>
       </c>
       <c r="I49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J49" s="3">
         <v>1200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1300</v>
       </c>
       <c r="K49" s="3">
         <v>1300</v>
       </c>
       <c r="L49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M49" s="3">
         <v>1400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1500</v>
       </c>
       <c r="N49" s="3">
         <v>1500</v>
       </c>
       <c r="O49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P49" s="3">
         <v>1600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1800</v>
       </c>
       <c r="R49" s="3">
         <v>1800</v>
       </c>
       <c r="S49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T49" s="3">
         <v>1900</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,62 +3641,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3500</v>
       </c>
       <c r="J52" s="3">
         <v>3500</v>
       </c>
       <c r="K52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L52" s="3">
         <v>3200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3100</v>
       </c>
       <c r="M52" s="3">
         <v>3100</v>
       </c>
       <c r="N52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>800</v>
       </c>
       <c r="R52" s="3">
         <v>800</v>
       </c>
       <c r="S52" s="3">
+        <v>800</v>
+      </c>
+      <c r="T52" s="3">
         <v>1700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>513100</v>
+      </c>
+      <c r="E54" s="3">
         <v>519400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>534000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>374100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>374400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>382900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>404700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>421100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>272400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>284500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>309300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>324000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>310900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>320900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>337000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>351500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>190600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +3921,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E57" s="3">
         <v>14800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,41 +3993,44 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>3600</v>
       </c>
       <c r="I58" s="3">
         <v>3600</v>
       </c>
       <c r="J58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E59" s="3">
         <v>18300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E60" s="3">
         <v>52100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>42800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>41400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13800</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,62 +4215,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E61" s="3">
         <v>77800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>78300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>78800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>77500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>80200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>78800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>49500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4146,19 +4289,22 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
       </c>
       <c r="F62" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>500</v>
@@ -4169,8 +4315,8 @@
       <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>500</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -4178,30 +4324,30 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>25800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E66" s="3">
         <v>130200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>131800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>132900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>122600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>118900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>124000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>121800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>116500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>111300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>71700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4721,11 +4889,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>328600</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-590300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-570700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-546000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-527100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-506200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-480500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-454600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-427100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-402400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-377200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-348700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-320500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-297900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-278700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-261500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-243200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-229100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>385800</v>
+      </c>
+      <c r="E76" s="3">
         <v>389200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>402200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>241200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>251800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>264000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>280800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>299400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>155900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>173100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>197100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>220800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>239200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>252800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>267100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>283300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-206300</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-25700</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,40 +5610,41 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
@@ -5454,7 +5653,7 @@
         <v>700</v>
       </c>
       <c r="P83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
@@ -5463,14 +5662,14 @@
         <v>800</v>
       </c>
       <c r="S83" s="3">
+        <v>800</v>
+      </c>
+      <c r="T83" s="3">
         <v>1800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,65 +6052,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-28100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-48300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,65 +6156,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,65 +6376,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6774,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>170500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>162100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>174100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>87400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>106800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6634,8 +6883,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6673,65 +6922,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>137000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>137400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>161300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>59100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>58200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,351 +656,363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E8" s="3">
         <v>83300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>69200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>68200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>53400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>44500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2400</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E9" s="3">
         <v>29300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E10" s="3">
         <v>54000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>43700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1300</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
       <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1040,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E12" s="3">
         <v>18200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>11600</v>
       </c>
       <c r="M12" s="3">
         <v>11600</v>
       </c>
       <c r="N12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="O12" s="3">
         <v>10700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1220,12 +1239,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1241,8 +1260,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1259,47 +1278,50 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E15" s="3">
         <v>1600</v>
       </c>
       <c r="F15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="3">
         <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="I15" s="3">
         <v>1300</v>
       </c>
       <c r="J15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1387,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E17" s="3">
         <v>106500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>101400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>96600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>87900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>80800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>80200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>72200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>73100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>60700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>58700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>55500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-25600</v>
       </c>
       <c r="M18" s="3">
         <v>-25600</v>
       </c>
       <c r="N18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="O18" s="3">
         <v>-28400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-47800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,13 +1577,14 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1559,11 +1592,11 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1571,12 +1604,12 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1584,37 +1617,37 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>1000</v>
       </c>
       <c r="Q20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1622,85 +1655,91 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-19900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-21100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-27600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-22700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-44900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1714,37 +1753,37 @@
         <v>900</v>
       </c>
       <c r="G22" s="3">
+        <v>900</v>
+      </c>
+      <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1000</v>
       </c>
       <c r="J22" s="3">
         <v>1000</v>
       </c>
       <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
         <v>1100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1000</v>
       </c>
       <c r="M22" s="3">
         <v>1000</v>
       </c>
       <c r="N22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="O22" s="3">
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1400</v>
       </c>
       <c r="R22" s="3">
         <v>1400</v>
@@ -1753,113 +1792,119 @@
         <v>1400</v>
       </c>
       <c r="T22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-18900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-53000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>200</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1870,8 +1915,8 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>400</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1891,8 +1936,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2055,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-27400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-53000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-27400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-53000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,13 +2535,16 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -2483,11 +2552,11 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -2495,12 +2564,12 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2508,37 +2577,37 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-1000</v>
       </c>
       <c r="Q32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2546,85 +2615,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-53000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2775,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-53000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,68 +3002,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>286500</v>
+      </c>
+      <c r="E41" s="3">
         <v>294300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>302700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>316200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>333700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>196800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>214100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>225600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>257200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>287100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>221900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>249200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>269800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>284300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>304300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>320500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>159200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,8 +3080,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,68 +3160,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E43" s="3">
         <v>84500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>80800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>79300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>83500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>69000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>34600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,67 +3240,70 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E44" s="3">
         <v>66700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>67000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>56200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>50900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>43900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>41600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>39800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>38900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>28500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>14000</v>
-      </c>
-      <c r="T44" s="3">
-        <v>10700</v>
       </c>
       <c r="U44" s="3">
         <v>10700</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
+      <c r="V44" s="3">
+        <v>10700</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
@@ -3225,68 +3320,71 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,68 +3400,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>450400</v>
+      </c>
+      <c r="E46" s="3">
         <v>454800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>458100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>465800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>481800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>323000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>321900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>329200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>350600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>368700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>230000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>245600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>272600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>288900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>298300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>308000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>326200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>339500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>176500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3417,8 +3521,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3456,8 +3560,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3465,59 +3572,59 @@
         <v>47900</v>
       </c>
       <c r="E48" s="3">
+        <v>47900</v>
+      </c>
+      <c r="F48" s="3">
         <v>46900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>49000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10500</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3542,59 +3652,59 @@
         <v>700</v>
       </c>
       <c r="E49" s="3">
+        <v>700</v>
+      </c>
+      <c r="F49" s="3">
         <v>800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>900</v>
       </c>
       <c r="G49" s="3">
         <v>900</v>
       </c>
       <c r="H49" s="3">
+        <v>900</v>
+      </c>
+      <c r="I49" s="3">
         <v>1000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1100</v>
       </c>
       <c r="J49" s="3">
         <v>1100</v>
       </c>
       <c r="K49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L49" s="3">
         <v>1200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1300</v>
       </c>
       <c r="M49" s="3">
         <v>1300</v>
       </c>
       <c r="N49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O49" s="3">
         <v>1400</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1500</v>
       </c>
       <c r="P49" s="3">
         <v>1500</v>
       </c>
       <c r="Q49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R49" s="3">
         <v>1600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1800</v>
       </c>
       <c r="T49" s="3">
         <v>1800</v>
       </c>
       <c r="U49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V49" s="3">
         <v>1900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,68 +3880,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3500</v>
       </c>
       <c r="L52" s="3">
         <v>3500</v>
       </c>
       <c r="M52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N52" s="3">
         <v>3200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>3100</v>
       </c>
       <c r="O52" s="3">
         <v>3100</v>
       </c>
       <c r="P52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>4000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>800</v>
       </c>
       <c r="T52" s="3">
         <v>800</v>
       </c>
       <c r="U52" s="3">
+        <v>800</v>
+      </c>
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,68 +4040,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>508100</v>
+      </c>
+      <c r="E54" s="3">
         <v>511500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>513100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>519400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>534000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>374100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>374400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>382900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>404700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>421100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>272400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>284500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>309300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>324000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>310900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>320900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>337000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>351500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>190600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,68 +4182,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E57" s="3">
         <v>11100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,47 +4260,50 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E58" s="3">
         <v>2100</v>
       </c>
       <c r="F58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G58" s="3">
         <v>4000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3600</v>
       </c>
       <c r="K58" s="3">
         <v>3600</v>
       </c>
       <c r="L58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M58" s="3">
         <v>1700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4207,68 +4340,71 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E59" s="3">
         <v>18800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18300</v>
       </c>
-      <c r="G59" s="3">
-        <v>11300</v>
-      </c>
       <c r="H59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I59" s="3">
         <v>15900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,68 +4420,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E60" s="3">
         <v>53900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>52100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13800</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,68 +4500,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E61" s="3">
         <v>76800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>77300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>77800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>78300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>78800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>79200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>77500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>79900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>80200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>78800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>49800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4438,25 +4580,28 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
       </c>
       <c r="H62" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>500</v>
@@ -4467,8 +4612,8 @@
       <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>500</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -4476,30 +4621,30 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>25800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,68 +4900,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E66" s="3">
         <v>131300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>127300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>130200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>131800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>132900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>122600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>118900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>124000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>121800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>116500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>111300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>112300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>71700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>68200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5063,11 +5230,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>328600</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,68 +5330,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-641600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-611700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-590300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-570700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-546000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-527100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-506200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-480500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-454600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-427100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-402400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-377200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-348700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-320500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-297900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-278700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-261500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-243200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-229100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,68 +5650,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>365900</v>
+      </c>
+      <c r="E76" s="3">
         <v>380300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>385800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>389200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>402200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>241200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>251800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>264000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>280800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>299400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>155900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>173100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>197100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>220800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>252800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>267100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>283300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-206300</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5810,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-53000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,46 +6007,47 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
         <v>1300</v>
       </c>
       <c r="F83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>700</v>
       </c>
       <c r="N83" s="3">
+        <v>700</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -5858,7 +6056,7 @@
         <v>700</v>
       </c>
       <c r="R83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="S83" s="3">
         <v>800</v>
@@ -5867,14 +6065,14 @@
         <v>800</v>
       </c>
       <c r="U83" s="3">
+        <v>800</v>
+      </c>
+      <c r="V83" s="3">
         <v>1800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2900</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5887,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-35900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-28100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-48300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6349,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,71 +6597,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,71 +6835,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6686,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6753,8 +6986,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,71 +7265,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>170500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>162100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>174100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>87400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>106800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7100,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7138,8 +7386,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7177,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>137000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>137400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-40900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>161300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>58200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>PRCT</t>
   </si>
@@ -656,363 +656,376 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E8" s="3">
         <v>76400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>69200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>68200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>53400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>44500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2400</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E9" s="3">
         <v>30100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4100</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E10" s="3">
         <v>46300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>51700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>44200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>43700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-1300</v>
       </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
       <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E12" s="3">
         <v>19100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>11600</v>
       </c>
       <c r="N12" s="3">
         <v>11600</v>
       </c>
       <c r="O12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="P12" s="3">
         <v>10700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,8 +1218,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1242,12 +1262,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1283,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1281,8 +1301,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1290,41 +1313,41 @@
         <v>1700</v>
       </c>
       <c r="E15" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F15" s="3">
         <v>1600</v>
       </c>
       <c r="G15" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H15" s="3">
         <v>1500</v>
       </c>
       <c r="I15" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
         <v>1300</v>
       </c>
       <c r="K15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E17" s="3">
         <v>107400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>106500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>101400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>87900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>80800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>80200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>72200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>73100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>60700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>55500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26000</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-22400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29600</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-25600</v>
       </c>
       <c r="N18" s="3">
         <v>-25600</v>
       </c>
       <c r="O18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="P18" s="3">
         <v>-28400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-24500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-47800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-23600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,41 +1611,42 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1620,37 +1654,37 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>1000</v>
       </c>
       <c r="R20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1658,93 +1692,99 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-21100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-27600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-22700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-44900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-22200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E22" s="3">
         <v>900</v>
@@ -1756,37 +1796,37 @@
         <v>900</v>
       </c>
       <c r="H22" s="3">
+        <v>900</v>
+      </c>
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>1000</v>
       </c>
       <c r="L22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M22" s="3">
         <v>1100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1000</v>
       </c>
       <c r="N22" s="3">
         <v>1000</v>
       </c>
       <c r="O22" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="P22" s="3">
         <v>900</v>
       </c>
       <c r="Q22" s="3">
+        <v>900</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1400</v>
       </c>
       <c r="S22" s="3">
         <v>1400</v>
@@ -1795,120 +1835,126 @@
         <v>1400</v>
       </c>
       <c r="U22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V22" s="3">
         <v>1500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-24700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-18500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-53000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,11 +1962,11 @@
         <v>3</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +1985,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-22600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-27400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-53000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-14100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-27400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-53000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,41 +2605,44 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2580,37 +2650,37 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-1000</v>
       </c>
       <c r="R32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2618,88 +2688,94 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-53000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-53000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,71 +3089,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>245600</v>
+      </c>
+      <c r="E41" s="3">
         <v>286500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>294300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>302700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>316200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>333700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>196800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>214100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>225600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>257200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>287100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>149700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>221900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>249200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>269800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>284300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>304300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>320500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>159200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,8 +3170,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3163,71 +3253,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E43" s="3">
         <v>83500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>84500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>83500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>69000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,70 +3336,73 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E44" s="3">
         <v>70700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>66700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>67000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>62300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>56200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>50900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>43900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>41600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>42600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>38900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>14000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>10700</v>
       </c>
       <c r="V44" s="3">
         <v>10700</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
+      <c r="W44" s="3">
+        <v>10700</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
@@ -3323,71 +3419,74 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,71 +3502,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E46" s="3">
         <v>450400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>454800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>458100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>465800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>481800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>323000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>321900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>329200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>350600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>368700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>230000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>245600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>272600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>288900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>298300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>308000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>326200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>339500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>176500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3524,8 +3629,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3563,71 +3668,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>47900</v>
+        <v>48900</v>
       </c>
       <c r="E48" s="3">
         <v>47900</v>
       </c>
       <c r="F48" s="3">
+        <v>47900</v>
+      </c>
+      <c r="G48" s="3">
         <v>46900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>48400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>47700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,71 +3751,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E49" s="3">
         <v>700</v>
       </c>
       <c r="F49" s="3">
+        <v>700</v>
+      </c>
+      <c r="G49" s="3">
         <v>800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>900</v>
       </c>
       <c r="H49" s="3">
         <v>900</v>
       </c>
       <c r="I49" s="3">
+        <v>900</v>
+      </c>
+      <c r="J49" s="3">
         <v>1000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1100</v>
       </c>
       <c r="K49" s="3">
         <v>1100</v>
       </c>
       <c r="L49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M49" s="3">
         <v>1200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1300</v>
       </c>
       <c r="N49" s="3">
         <v>1300</v>
       </c>
       <c r="O49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P49" s="3">
         <v>1400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1500</v>
       </c>
       <c r="Q49" s="3">
         <v>1500</v>
       </c>
       <c r="R49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S49" s="3">
         <v>1600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1800</v>
       </c>
       <c r="U49" s="3">
         <v>1800</v>
       </c>
       <c r="V49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W49" s="3">
         <v>1900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,71 +4000,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3500</v>
       </c>
       <c r="M52" s="3">
         <v>3500</v>
       </c>
       <c r="N52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O52" s="3">
         <v>3200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>3100</v>
       </c>
       <c r="P52" s="3">
         <v>3100</v>
       </c>
       <c r="Q52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="R52" s="3">
         <v>4000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>800</v>
       </c>
       <c r="U52" s="3">
         <v>800</v>
       </c>
       <c r="V52" s="3">
+        <v>800</v>
+      </c>
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,71 +4166,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>487100</v>
+      </c>
+      <c r="E54" s="3">
         <v>508100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>511500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>513100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>519400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>534000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>374100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>374400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>382900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>404700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>421100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>272400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>284500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>309300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>324000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>310900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>320900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>337000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>351500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>190600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,71 +4313,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E57" s="3">
         <v>17300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,50 +4394,53 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2100</v>
       </c>
       <c r="F58" s="3">
         <v>2100</v>
       </c>
       <c r="G58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H58" s="3">
         <v>4000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3600</v>
       </c>
       <c r="L58" s="3">
         <v>3600</v>
       </c>
       <c r="M58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N58" s="3">
         <v>1700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4343,71 +4477,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,71 +4560,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E60" s="3">
         <v>65800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>52100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>42800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>35300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13800</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,71 +4643,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E61" s="3">
         <v>76300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>76800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>77300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>77800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>78300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>78800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>79700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>77500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>79900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>80200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>50000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>49500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4583,8 +4726,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4592,19 +4738,19 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
+        <v>100</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
       </c>
       <c r="I62" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J62" s="3">
         <v>500</v>
@@ -4615,8 +4761,8 @@
       <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>500</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -4624,30 +4770,30 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>25800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,71 +5058,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E66" s="3">
         <v>142200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>131300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>127300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>130200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>131800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>132900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>122600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>118900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>124000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>121800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>116500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>111300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>103300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>71700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>68300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5233,11 +5401,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>328600</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,71 +5504,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-673200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-641600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-611700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-590300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-570700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-546000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-527100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-506200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-480500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-454600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-427100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-402400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-377200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-348700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-320500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-297900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-278700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-261500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-243200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-229100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,71 +5836,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>347700</v>
+      </c>
+      <c r="E76" s="3">
         <v>365900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>380300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>385800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>389200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>402200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>241200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>251800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>264000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>280800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>299400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>155900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>173100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>197100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>220800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>239200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>252800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>267100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>283300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-206300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-53000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,49 +6206,50 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1300</v>
       </c>
       <c r="F83" s="3">
         <v>1300</v>
       </c>
       <c r="G83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
       </c>
       <c r="O83" s="3">
+        <v>700</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>700</v>
       </c>
       <c r="Q83" s="3">
         <v>700</v>
@@ -6059,7 +6258,7 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="T83" s="3">
         <v>800</v>
@@ -6068,14 +6267,14 @@
         <v>800</v>
       </c>
       <c r="V83" s="3">
+        <v>800</v>
+      </c>
+      <c r="W83" s="3">
         <v>1800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-32300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-35900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-28100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-48300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,74 +6818,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7065,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6989,8 +7223,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7511,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>170500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>162100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>174100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>87400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>106800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,8 +7594,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7389,8 +7638,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>137000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>137400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-40900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>161300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>58200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
